--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_medianeta_a_2022_maule.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_medianeta_a_2022_maule.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:41</t>
+    <t xml:space="preserve">2026-09-24 01:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -736,13 +736,13 @@
         <v>30</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>0.13</v>
+        <v>0.09</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="11">
@@ -759,13 +759,13 @@
         <v>30</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.09</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="12">
@@ -782,13 +782,13 @@
         <v>30</v>
       </c>
       <c r="E12" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>335</v>
+      </c>
+      <c r="G12" s="2" t="n">
         <v>0.16</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>332</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>0.13</v>
       </c>
     </row>
     <row r="13">
@@ -799,19 +799,19 @@
         <v>19</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="14">
@@ -845,19 +845,19 @@
         <v>25</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.27</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.06</v>
+        <v>0.15</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="16">
@@ -868,19 +868,19 @@
         <v>25</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.11</v>
+        <v>0.07</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-0.09</v>
+        <v>0.02</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.19</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="17">
@@ -891,19 +891,19 @@
         <v>25</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-0.37</v>
+        <v>-0.48</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.14</v>
+        <v>0.23</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-0.51</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="18">
